--- a/cumpleanos.xlsx
+++ b/cumpleanos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="253" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0DEB808-C5FE-4797-A27F-0058A7171A43}"/>
+  <xr:revisionPtr revIDLastSave="257" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4B2E139-368B-4D9B-876C-57EE9979253C}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1836" yWindow="1836" windowWidth="17256" windowHeight="8856" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -77,15 +77,9 @@
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>JOSE</t>
-  </si>
-  <si>
     <t>VIRGO</t>
   </si>
   <si>
-    <t>SANDRA</t>
-  </si>
-  <si>
     <t>ESCORPION</t>
   </si>
   <si>
@@ -111,6 +105,12 @@
   </si>
   <si>
     <t>CORELLA FERNANDO</t>
+  </si>
+  <si>
+    <t>SANDRA E.</t>
+  </si>
+  <si>
+    <t>SANDRA O.</t>
   </si>
 </sst>
 </file>
@@ -536,10 +536,10 @@
   <sheetData>
     <row r="1" spans="1:6" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="2" spans="1:6" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="6">
         <v>46044</v>
@@ -624,7 +624,7 @@
     </row>
     <row r="9" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" s="6">
         <v>46242</v>
@@ -647,57 +647,57 @@
     </row>
     <row r="11" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46281</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="B11" s="6">
-        <v>46271</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B12" s="6">
         <v>46326</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13" s="6">
         <v>46361</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B14" s="6">
         <v>46361</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B15" s="6">
         <v>46373</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/cumpleanos.xlsx
+++ b/cumpleanos.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="257" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4B2E139-368B-4D9B-876C-57EE9979253C}"/>
+  <xr:revisionPtr revIDLastSave="298" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E0E1051-155D-4E8A-A650-E8A9FED10769}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Programas" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
   <si>
     <t>SIGNO</t>
   </si>
@@ -111,13 +112,59 @@
   </si>
   <si>
     <t>SANDRA O.</t>
+  </si>
+  <si>
+    <t>Cuenta</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Programa</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Aprobado</t>
+  </si>
+  <si>
+    <t>Postulado</t>
+  </si>
+  <si>
+    <t>Jenifer Rodriguez</t>
+  </si>
+  <si>
+    <t>FA FOR COPILOT: AGENT SOLUTION DEPLOYMENT ACCELERATOR</t>
+  </si>
+  <si>
+    <t>JGB</t>
+  </si>
+  <si>
+    <t>William Correa</t>
+  </si>
+  <si>
+    <t>ENERTOTAL</t>
+  </si>
+  <si>
+    <t>COEXITO</t>
+  </si>
+  <si>
+    <t>AGECOLDEX</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,13 +187,34 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -173,10 +241,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -192,8 +261,14 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -704,4 +779,138 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91859155-B788-4D02-B0C0-8BFEB74B5DDC}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="9">
+        <v>2000</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="9">
+        <v>2000</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="9">
+        <v>2000</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="9">
+        <v>2000</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/cumpleanos.xlsx
+++ b/cumpleanos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="298" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E0E1051-155D-4E8A-A650-E8A9FED10769}"/>
+  <xr:revisionPtr revIDLastSave="299" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{147D8099-1AD9-4F71-B40B-2DA2CA5F2629}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
+    <workbookView minimized="1" xWindow="3384" yWindow="3384" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -162,7 +162,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -265,7 +265,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -855,7 +855,7 @@
         <v>2000</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">

--- a/cumpleanos.xlsx
+++ b/cumpleanos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="299" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{147D8099-1AD9-4F71-B40B-2DA2CA5F2629}"/>
+  <xr:revisionPtr revIDLastSave="330" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A1AAB0B-6624-4919-A199-E38F7298ED97}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3384" yWindow="3384" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="46">
   <si>
     <t>SIGNO</t>
   </si>
@@ -129,24 +129,12 @@
     <t>Estado</t>
   </si>
   <si>
-    <t>Aprobado</t>
-  </si>
-  <si>
-    <t>Postulado</t>
-  </si>
-  <si>
-    <t>Jenifer Rodriguez</t>
-  </si>
-  <si>
     <t>FA FOR COPILOT: AGENT SOLUTION DEPLOYMENT ACCELERATOR</t>
   </si>
   <si>
     <t>JGB</t>
   </si>
   <si>
-    <t>William Correa</t>
-  </si>
-  <si>
     <t>ENERTOTAL</t>
   </si>
   <si>
@@ -154,6 +142,39 @@
   </si>
   <si>
     <t>AGECOLDEX</t>
+  </si>
+  <si>
+    <t>IMECOL</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ JENIFER</t>
+  </si>
+  <si>
+    <t>CORREA WILLIAM</t>
+  </si>
+  <si>
+    <t>COLOMBINA</t>
+  </si>
+  <si>
+    <t>OFRECIDO</t>
+  </si>
+  <si>
+    <t>POSTULADO</t>
+  </si>
+  <si>
+    <t>APROBADO</t>
+  </si>
+  <si>
+    <t>DOMINIO</t>
+  </si>
+  <si>
+    <t>AIBS</t>
+  </si>
+  <si>
+    <t>OCAMPO SANDRA</t>
+  </si>
+  <si>
+    <t>ECHEVERRY SANDRA</t>
   </si>
 </sst>
 </file>
@@ -783,14 +804,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91859155-B788-4D02-B0C0-8BFEB74B5DDC}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>25</v>
       </c>
@@ -798,117 +821,161 @@
         <v>26</v>
       </c>
       <c r="C1" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="9">
+        <v>2000</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="9">
+        <v>2000</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="9">
+        <v>2000</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="9">
+        <v>2000</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="9">
+        <v>2000</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="9">
+      <c r="B7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="9">
         <v>2000</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="9">
-        <v>2000</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="9">
-        <v>2000</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="9">
-        <v>2000</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D8" s="7"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D9" s="7"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cumpleanos.xlsx
+++ b/cumpleanos.xlsx
@@ -8,14 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="330" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A1AAB0B-6624-4919-A199-E38F7298ED97}"/>
+  <xr:revisionPtr revIDLastSave="414" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A501006-762B-43FC-A740-9783AF23D8D6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Programas" sheetId="2" r:id="rId2"/>
+    <sheet name="IN30" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IN30'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Programas!$A$1:$F$10</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="68">
   <si>
     <t>SIGNO</t>
   </si>
@@ -147,6 +152,9 @@
     <t>IMECOL</t>
   </si>
   <si>
+    <t>SANDRA OCAMPO</t>
+  </si>
+  <si>
     <t>RODRIGUEZ JENIFER</t>
   </si>
   <si>
@@ -175,6 +183,69 @@
   </si>
   <si>
     <t>ECHEVERRY SANDRA</t>
+  </si>
+  <si>
+    <t>CLIENTE</t>
+  </si>
+  <si>
+    <t>ACTIVIDAD</t>
+  </si>
+  <si>
+    <t>ESTADO</t>
+  </si>
+  <si>
+    <t>COEM BACKUP IN 30</t>
+  </si>
+  <si>
+    <t>COPILOT IN 30</t>
+  </si>
+  <si>
+    <t>COMFANDI</t>
+  </si>
+  <si>
+    <t>ASSESSMENT SEGURIDAD</t>
+  </si>
+  <si>
+    <t>EFICACIA</t>
+  </si>
+  <si>
+    <t>USC</t>
+  </si>
+  <si>
+    <t>INCAUCA Y PROVIDENCIA</t>
+  </si>
+  <si>
+    <t>COMERCIAL</t>
+  </si>
+  <si>
+    <t>ROMY MENDOZA</t>
+  </si>
+  <si>
+    <t>WILLIAM CORREA</t>
+  </si>
+  <si>
+    <t>JENIFER RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>CHIPICHAPE</t>
+  </si>
+  <si>
+    <t>BMM</t>
+  </si>
+  <si>
+    <t>MENDOZA ROMY</t>
+  </si>
+  <si>
+    <t>SECURITY</t>
+  </si>
+  <si>
+    <t>FA FOR SECURITY: ENVISIONING &amp; POC ME3/ME5</t>
+  </si>
+  <si>
+    <t>FA FOR COPILOT: ENVISIONING &amp; POC</t>
+  </si>
+  <si>
+    <t>COPILOT: COWORK &amp; AGENT SOL DEPLOY ACC</t>
   </si>
 </sst>
 </file>
@@ -266,7 +337,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -287,6 +358,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -804,7 +876,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91859155-B788-4D02-B0C0-8BFEB74B5DDC}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
@@ -821,7 +893,7 @@
         <v>26</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>27</v>
@@ -838,10 +910,10 @@
         <v>34</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>30</v>
@@ -850,24 +922,24 @@
         <v>2000</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="E3" s="9">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>40</v>
@@ -875,33 +947,33 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E4" s="9">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>30</v>
@@ -910,18 +982,18 @@
         <v>2000</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>30</v>
@@ -930,54 +1002,309 @@
         <v>2000</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="9">
+        <v>3000</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>38</v>
       </c>
+      <c r="C8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="9">
+        <v>2000</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="9">
+        <v>2000</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="9">
+        <v>2000</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F10" xr:uid="{91859155-B788-4D02-B0C0-8BFEB74B5DDC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F10">
+      <sortCondition ref="A1:A10"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F78C39-4CA6-469E-83D6-D031732ACDDC}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="B7" s="7" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="9">
-        <v>2000</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D8" xr:uid="{79F78C39-4CA6-469E-83D6-D031732ACDDC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D8">
+      <sortCondition ref="A1:A8"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/cumpleanos.xlsx
+++ b/cumpleanos.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="414" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A501006-762B-43FC-A740-9783AF23D8D6}"/>
+  <xr:revisionPtr revIDLastSave="454" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D282F32-3388-4E9A-AFCD-4ACA86061118}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
+    <workbookView minimized="1" xWindow="3384" yWindow="3384" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Programas" sheetId="2" r:id="rId2"/>
-    <sheet name="IN30" sheetId="3" r:id="rId3"/>
+    <sheet name="baseCopilotIN30" sheetId="4" r:id="rId3"/>
+    <sheet name="IN30" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IN30'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'IN30'!$A$1:$D$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Programas!$A$1:$F$10</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="88">
   <si>
     <t>SIGNO</t>
   </si>
@@ -164,6 +165,9 @@
     <t>COLOMBINA</t>
   </si>
   <si>
+    <t>SANDRA ECHEVERRY</t>
+  </si>
+  <si>
     <t>OFRECIDO</t>
   </si>
   <si>
@@ -246,6 +250,63 @@
   </si>
   <si>
     <t>COPILOT: COWORK &amp; AGENT SOL DEPLOY ACC</t>
+  </si>
+  <si>
+    <t>CUSTOMER</t>
+  </si>
+  <si>
+    <t>CANTIDAD BUSINESS</t>
+  </si>
+  <si>
+    <t>CANTIDAD COPILOT</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Agraf Industrial</t>
+  </si>
+  <si>
+    <t>Agricolas Capital Group</t>
+  </si>
+  <si>
+    <t>Alfredo Lopez &amp; Cia</t>
+  </si>
+  <si>
+    <t>ARQUITECTURA Y CONCRETO S.A.S</t>
+  </si>
+  <si>
+    <t>Bioart</t>
+  </si>
+  <si>
+    <t>Central Control SAS (Jardin Plaza)</t>
+  </si>
+  <si>
+    <t>Colegios Comfandi</t>
+  </si>
+  <si>
+    <t>COMERCIALIZADORA AGROPARTS S.A.S.</t>
+  </si>
+  <si>
+    <t>ENERTOTAL S.A. E.S.P.</t>
+  </si>
+  <si>
+    <t>Fragancias y Sabores</t>
+  </si>
+  <si>
+    <t>Health Company SAS</t>
+  </si>
+  <si>
+    <t>Ingeniopichichi.com</t>
+  </si>
+  <si>
+    <t>INPEL SA</t>
+  </si>
+  <si>
+    <t>RESEARCH PHARMACEUTICAL S.A.</t>
+  </si>
+  <si>
+    <t>TUCASH S.A.S</t>
   </si>
 </sst>
 </file>
@@ -256,7 +317,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,8 +355,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,8 +377,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -332,12 +407,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -359,6 +458,13 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -893,7 +999,7 @@
         <v>26</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>27</v>
@@ -913,7 +1019,7 @@
         <v>37</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>30</v>
@@ -922,47 +1028,47 @@
         <v>2000</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>38</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E3" s="9">
         <v>1500</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>38</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E4" s="9">
         <v>4000</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -973,7 +1079,7 @@
         <v>37</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>30</v>
@@ -982,7 +1088,7 @@
         <v>2000</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -990,10 +1096,10 @@
         <v>39</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>30</v>
@@ -1002,27 +1108,27 @@
         <v>2000</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E7" s="9">
         <v>3000</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1033,7 +1139,7 @@
         <v>38</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>30</v>
@@ -1042,7 +1148,7 @@
         <v>2000</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1050,10 +1156,10 @@
         <v>35</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>30</v>
@@ -1062,7 +1168,7 @@
         <v>2000</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1073,7 +1179,7 @@
         <v>38</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>30</v>
@@ -1082,7 +1188,7 @@
         <v>2000</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1136,6 +1242,295 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92E079F1-F6C1-4D19-AB88-F9033B363627}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="15">
+        <v>66</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0</v>
+      </c>
+      <c r="E2" s="15">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="15">
+        <v>27</v>
+      </c>
+      <c r="D3" s="15">
+        <v>1</v>
+      </c>
+      <c r="E3" s="15">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="15">
+        <v>39</v>
+      </c>
+      <c r="D4" s="15">
+        <v>0</v>
+      </c>
+      <c r="E4" s="15">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="15">
+        <v>0</v>
+      </c>
+      <c r="D5" s="15">
+        <v>3</v>
+      </c>
+      <c r="E5" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="15">
+        <v>135</v>
+      </c>
+      <c r="D6" s="15">
+        <v>1</v>
+      </c>
+      <c r="E6" s="15">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="15">
+        <v>98</v>
+      </c>
+      <c r="D7" s="15">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="15">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15">
+        <v>2</v>
+      </c>
+      <c r="E8" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="15">
+        <v>30</v>
+      </c>
+      <c r="D9" s="15">
+        <v>0</v>
+      </c>
+      <c r="E9" s="15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="15">
+        <v>176</v>
+      </c>
+      <c r="D10" s="15">
+        <v>7</v>
+      </c>
+      <c r="E10" s="15">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="15">
+        <v>58</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="15">
+        <v>62</v>
+      </c>
+      <c r="D12" s="15">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="15">
+        <v>268</v>
+      </c>
+      <c r="D13" s="15">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="15">
+        <v>38</v>
+      </c>
+      <c r="D14" s="15">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="15">
+        <v>34</v>
+      </c>
+      <c r="D15" s="15">
+        <v>0</v>
+      </c>
+      <c r="E15" s="15">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="15">
+        <v>29</v>
+      </c>
+      <c r="D16" s="15">
+        <v>0</v>
+      </c>
+      <c r="E16" s="15">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F78C39-4CA6-469E-83D6-D031732ACDDC}">
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1147,58 +1542,58 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>60</v>
-      </c>
       <c r="C2" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>53</v>
-      </c>
       <c r="D4" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1209,52 +1604,52 @@
         <v>36</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">

--- a/cumpleanos.xlsx
+++ b/cumpleanos.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="454" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D282F32-3388-4E9A-AFCD-4ACA86061118}"/>
+  <xr:revisionPtr revIDLastSave="465" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{835F4885-0404-4A34-A10B-D5C7B142D92B}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3384" yWindow="3384" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Programas" sheetId="2" r:id="rId2"/>
     <sheet name="baseCopilotIN30" sheetId="4" r:id="rId3"/>
     <sheet name="IN30" sheetId="3" r:id="rId4"/>
+    <sheet name="Azure" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'IN30'!$A$1:$D$8</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="111">
   <si>
     <t>SIGNO</t>
   </si>
@@ -228,6 +229,9 @@
     <t>WILLIAM CORREA</t>
   </si>
   <si>
+    <t>VATIA</t>
+  </si>
+  <si>
     <t>JENIFER RODRIGUEZ</t>
   </si>
   <si>
@@ -307,6 +311,72 @@
   </si>
   <si>
     <t>TUCASH S.A.S</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>SEGMENTO</t>
+  </si>
+  <si>
+    <t>CONTRATO</t>
+  </si>
+  <si>
+    <t>MES RENOVACIÓN</t>
+  </si>
+  <si>
+    <t>Corporate</t>
+  </si>
+  <si>
+    <t>CHRISTUS SINERGIA</t>
+  </si>
+  <si>
+    <t>CSP Azure</t>
+  </si>
+  <si>
+    <t>Marzo</t>
+  </si>
+  <si>
+    <t>CSP Azure - Mensual</t>
+  </si>
+  <si>
+    <t>Diciembre</t>
+  </si>
+  <si>
+    <t>Romy Mendoza</t>
+  </si>
+  <si>
+    <t>STUDIO F</t>
+  </si>
+  <si>
+    <t>Enero</t>
+  </si>
+  <si>
+    <t>SMB</t>
+  </si>
+  <si>
+    <t>SISTEMAS DE INFORMACION EMPRESARIAL -SIESA</t>
+  </si>
+  <si>
+    <t>Sergio Castro</t>
+  </si>
+  <si>
+    <t>INVERSIONES MANUELITA</t>
+  </si>
+  <si>
+    <t>SPRBN - Azure</t>
+  </si>
+  <si>
+    <t>EA Azure</t>
+  </si>
+  <si>
+    <t>Septiembre</t>
+  </si>
+  <si>
+    <t>Renovación</t>
+  </si>
+  <si>
+    <t>Sandra Echeverry</t>
   </si>
 </sst>
 </file>
@@ -317,7 +387,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -363,8 +433,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -381,6 +463,24 @@
       <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F75B5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BC2E6"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -436,7 +536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -464,6 +564,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1033,7 +1145,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>38</v>
@@ -1042,7 +1154,7 @@
         <v>45</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E3" s="9">
         <v>1500</v>
@@ -1053,16 +1165,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>38</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E4" s="9">
         <v>4000</v>
@@ -1116,13 +1228,13 @@
         <v>53</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>45</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E7" s="9">
         <v>3000</v>
@@ -1255,27 +1367,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>58</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C2" s="15">
         <v>66</v>
@@ -1289,10 +1401,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" s="15">
         <v>27</v>
@@ -1306,10 +1418,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="15">
         <v>39</v>
@@ -1323,10 +1435,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="15">
         <v>0</v>
@@ -1340,7 +1452,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>40</v>
@@ -1357,10 +1469,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7" s="15">
         <v>98</v>
@@ -1374,7 +1486,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>59</v>
@@ -1391,10 +1503,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" s="15">
         <v>30</v>
@@ -1408,7 +1520,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>60</v>
@@ -1425,10 +1537,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" s="15">
         <v>58</v>
@@ -1442,10 +1554,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" s="15">
         <v>62</v>
@@ -1459,7 +1571,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>60</v>
@@ -1476,10 +1588,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" s="15">
         <v>38</v>
@@ -1493,10 +1605,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="15">
         <v>34</v>
@@ -1510,10 +1622,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C16" s="15">
         <v>29</v>
@@ -1556,10 +1668,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>61</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>51</v>
@@ -1702,4 +1814,182 @@
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5F14E09-6602-4742-8047-FC3F44914325}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>